--- a/upload/tu-vung-hsk1-mau_426-tu_dich-nghia-cau-chinh-xac.xlsx
+++ b/upload/tu-vung-hsk1-mau_426-tu_dich-nghia-cau-chinh-xac.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3065" uniqueCount="2523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3085" uniqueCount="2542">
   <si>
     <t>STT</t>
   </si>
@@ -7635,12 +7635,69 @@
   <si>
     <t>Anh ấy + 亻bộ nhân 门 bộ môn (cửa) → họ</t>
   </si>
+  <si>
+    <t>喜 (士: kẻ sĩ + 口: miệng + 丷: tám + 豆: đậu) + 欢 (又: tay phải + 欠: thiếu, ngáp)</t>
+  </si>
+  <si>
+    <t>爫 (móng vuốt/tay) + 冖 (mái che) + 友 (bạn bè)</t>
+  </si>
+  <si>
+    <t>开 (廾: hai tay + 一: nét ngang) + 心 (tim, lòng)</t>
+  </si>
+  <si>
+    <t>难 (又: tay phải + 隹: chim) + 过 (辶: bộ sước, đi + 寸: tấc)</t>
+  </si>
+  <si>
+    <t>讨 (讠: bộ ngôn, lời nói + 寸: tấc) + 厌 (厂: vách núi + 犬: chó)</t>
+  </si>
+  <si>
+    <t>放 (方: phương, vuông + 攵: bộ phộc, đánh/gõ) + 心 (tim, lòng)</t>
+  </si>
+  <si>
+    <t>安 (宀: bộ miên, mái nhà + 女: phụ nữ) + 心 (tim, lòng)</t>
+  </si>
+  <si>
+    <t>好 (女: phụ nữ + 子: con) + 讨厌 (ghét)</t>
+  </si>
+  <si>
+    <t>Cảm thấy rất ghét → đáng ghét quá</t>
+  </si>
+  <si>
+    <t>最 (日: mặt trời + 取: lấy) + 讨厌 (ghét)</t>
+  </si>
+  <si>
+    <t>最 (日: mặt trời + 取: lấy) + 喜欢 (thích)</t>
+  </si>
+  <si>
+    <t>士 người nói chuyện 口, người lắng tai nghe và nói lại 口, thích nắm tay 又 che chở cho người mình thích 欠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">爫 bắt đầu nắm 1 tay che chở 冖 nắm 2 tay 友 </t>
+  </si>
+  <si>
+    <t>Mở rộng trái tim → cảm thấy vui</t>
+  </si>
+  <si>
+    <t>讠nói ra bị chặn lại 寸, 犬 con chó núp ở vách núi k thèm nói  chuyện =&gt;ghét</t>
+  </si>
+  <si>
+    <t>1 tay 又 bắt chim 隹 càng khó, bước đi 辶 cũng bị chặn 寸 =&gt; buồn</t>
+  </si>
+  <si>
+    <t>Bỏ dao 方 buông tay 攵   trong tâm 心→ yên tâm</t>
+  </si>
+  <si>
+    <t>女 có phụ nữ ở trong nhà 宀 trong lòng thấy an tâm 心 → an tâm</t>
+  </si>
+  <si>
+    <t>dùng tai 耳 👂và tay 又 ✋ chọn ra 1 thứ nổi bật nhất =&gt; nhất</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7661,6 +7718,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -7670,7 +7741,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -7693,16 +7764,240 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8008,623 +8303,683 @@
   <dimension ref="A1:J427"/>
   <sheetFormatPr defaultColWidth="24.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="53.85546875" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" customWidth="1"/>
     <col min="9" max="9" width="38.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="52.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="12" t="s">
         <v>2501</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="12" t="s">
         <v>2502</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="14" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>2503</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>2504</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>2515</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>2505</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>2506</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>2514</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>2507</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>2508</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>2509</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>2510</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>2518</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>2520</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>2517</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>2521</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="7" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>2519</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>2522</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>2511</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>2512</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="16" t="s">
         <v>2513</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="16" t="s">
         <v>2516</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="17" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E12" t="s">
+      <c r="C12" s="4" t="s">
+        <v>2523</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>2534</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E13" t="s">
+      <c r="C13" s="2" t="s">
+        <v>2524</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>2535</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="7" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E14" t="s">
+      <c r="C14" s="2" t="s">
+        <v>2525</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>2536</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E15" t="s">
+      <c r="C15" s="2" t="s">
+        <v>2526</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>2538</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="7" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E16" t="s">
+      <c r="C16" s="2" t="s">
+        <v>2527</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E17" t="s">
+      <c r="C17" s="2" t="s">
+        <v>2528</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2539</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="7" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E18" t="s">
+      <c r="C18" s="2" t="s">
+        <v>2529</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>2540</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E19" t="s">
+      <c r="C19" s="2" t="s">
+        <v>2530</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>2531</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E20" t="s">
+      <c r="C20" s="2" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21">
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E21" t="s">
+      <c r="C21" s="9" t="s">
+        <v>2533</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="10" t="s">
         <v>128</v>
       </c>
     </row>
@@ -19195,6 +19550,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
